--- a/Result/profitability/9908.xlsx
+++ b/Result/profitability/9908.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38125</v>
+        <v>0.3975</v>
       </c>
       <c r="N2" t="n">
-        <v>20.95625</v>
+        <v>21.1825</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32125</v>
+        <v>0.39625</v>
       </c>
       <c r="N3" t="n">
-        <v>19.98625</v>
+        <v>20.9975</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0.35375</v>
+        <v>0.4149999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>19.70875</v>
+        <v>20.0625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3337499999999999</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>18.27375</v>
+        <v>18.0925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2812499999999999</v>
+        <v>0.275</v>
       </c>
       <c r="N6" t="n">
-        <v>16.705</v>
+        <v>16.83125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2425</v>
+        <v>0.31625</v>
       </c>
       <c r="N7" t="n">
-        <v>15.83</v>
+        <v>16.57</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.25</v>
+        <v>0.305</v>
       </c>
       <c r="N8" t="n">
-        <v>15.39125</v>
+        <v>15.84625</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9908</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>853</v>
+      </c>
+      <c r="D75" t="n">
+        <v>639</v>
+      </c>
+      <c r="E75" t="n">
+        <v>214</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>147</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>17.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>317</v>
+      </c>
+      <c r="J75" t="n">
+        <v>464</v>
+      </c>
+      <c r="K75" t="n">
+        <v>387</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.34875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.639999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.169776119402985</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.450000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05465510742555613</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
